--- a/data/trans_orig/P5B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>49066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55325</t>
+          <t>55225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45364</t>
+          <t>44937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>50699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97430</t>
+          <t>97064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104949</t>
+          <t>105013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291264</t>
+          <t>290979</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>302688</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336489</t>
+          <t>337943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>346949</t>
+          <t>347179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>632308</t>
+          <t>632443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>647526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128590</t>
+          <t>128895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135267</t>
+          <t>135343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117288</t>
+          <t>117230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122906</t>
+          <t>122921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249144</t>
+          <t>249167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257252</t>
+          <t>257429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>477003</t>
+          <t>475156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490538</t>
+          <t>489746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>505845</t>
+          <t>504686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>518437</t>
+          <t>517976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>985522</t>
+          <t>987183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1004624</t>
+          <t>1005296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51560</t>
+          <t>52021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57706</t>
+          <t>57632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112354</t>
+          <t>111924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116976</t>
+          <t>116967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>17083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294577</t>
+          <t>294171</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>302156</t>
+          <t>302054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329169</t>
+          <t>329191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337109</t>
+          <t>337133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627388</t>
+          <t>626861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>638292</t>
+          <t>637743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>107922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>114638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130021</t>
+          <t>130037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240246</t>
+          <t>241078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248886</t>
+          <t>248882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>460636</t>
+          <t>459603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>470370</t>
+          <t>470548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522941</t>
+          <t>523240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>532817</t>
+          <t>532717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>986914</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1001509</t>
+          <t>1001007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36291</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>46493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86186</t>
+          <t>85857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91259</t>
+          <t>91231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332964</t>
+          <t>332669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342049</t>
+          <t>341687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372488</t>
+          <t>372334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378423</t>
+          <t>378506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708651</t>
+          <t>708823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718953</t>
+          <t>719081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133941</t>
+          <t>133729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139286</t>
+          <t>139281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269626</t>
+          <t>269341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275957</t>
+          <t>275311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507503</t>
+          <t>507805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517360</t>
+          <t>517515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>558749</t>
+          <t>558539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>567061</t>
+          <t>567203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070614</t>
+          <t>1071278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1083167</t>
+          <t>1083334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>533</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50869</t>
+          <t>50231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>55942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61458</t>
+          <t>61471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109517</t>
+          <t>109116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115823</t>
+          <t>115812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128745</t>
+          <t>112153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129511</t>
+          <t>178585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>348357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458177</t>
+          <t>458133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509893</t>
+          <t>509633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516031</t>
+          <t>515531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>847618</t>
+          <t>798544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972693</t>
+          <t>972242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146045</t>
+          <t>145462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171150</t>
+          <t>171418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180199</t>
+          <t>179836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319583</t>
+          <t>319427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328220</t>
+          <t>328114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111418</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121689</t>
+          <t>157028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>552564</t>
+          <t>542134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>660599</t>
+          <t>660573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743268</t>
+          <t>744313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>755109</t>
+          <t>754731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1302623</t>
+          <t>1267284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1411867</t>
+          <t>1411421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5B_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2598</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6674</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3360</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7396</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7229</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48773</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44697</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50706</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53102</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49066</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55225</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49233</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55222</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48773</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44937</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>50699</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97064</t>
+          <t>97290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105013</t>
+          <t>104714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16461</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12380</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7929</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19338</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19136</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6457</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15693</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31510</t>
+          <t>31416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>342829</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>337175</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>347269</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>447</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>297937</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>290979</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>302388</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>291181</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>303125</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>342829</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>337943</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>347179</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>632443</t>
+          <t>632537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>647526</t>
+          <t>647602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6853</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3535</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7686</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7939</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6312</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121028</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>116689</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122899</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>133046</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>128895</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135343</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>128642</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>135249</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>121028</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>117230</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>122921</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249167</t>
+          <t>249228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>257429</t>
+          <t>257403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9852</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23333</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13613</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28203</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13041</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27491</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10573</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23863</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>512630</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>505216</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>518697</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>484084</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>475156</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>489746</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>475868</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>490318</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>512630</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>504686</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>517976</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>987183</t>
+          <t>987481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1005296</t>
+          <t>1005750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3463</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3842</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4458</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60826</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57708</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54789</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52021</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51642</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60826</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57632</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>166</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111924</t>
+          <t>112370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116967</t>
+          <t>116971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5569</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4779</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9980</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2152</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9464</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2660</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10602</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>334224</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>329476</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>337149</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>433</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>299372</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>294171</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>302054</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>294687</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>301999</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>334224</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>329191</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>337133</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>626861</t>
+          <t>627584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>637743</t>
+          <t>638280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>440</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304151</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304151</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304151</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4162</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1455</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8793</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5392</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133914</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130491</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135429</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>111931</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107922</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>114638</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107300</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114541</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>133914</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130037</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>135429</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241078</t>
+          <t>240452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248882</t>
+          <t>249114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>135429</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>135429</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>135429</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116093</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116093</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>135429</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>135429</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>135429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16126</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15733</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14072</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>528963</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>522496</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>532574</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>466093</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>459603</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>470548</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>459996</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>470127</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>528963</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>523240</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>532717</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>986122</t>
+          <t>987717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1001007</t>
+          <t>1000735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>475729</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>475729</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>475729</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3934,67 +3934,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1228</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4744</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49957</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46746</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39413</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36580</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36471</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49957</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46493</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>134</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85857</t>
+          <t>85863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91231</t>
+          <t>91218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8129</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13612</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13052</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6854</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>376469</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>372009</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>378598</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>338152</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>332669</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>341687</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>333229</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>341978</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>376469</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>372334</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>378506</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708823</t>
+          <t>708446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>719081</t>
+          <t>718814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379188</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379188</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379188</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>521</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>346281</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>346281</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>346281</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379188</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379188</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,92 +4615,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2301</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137629</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133901</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139284</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>137629</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>133729</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139281</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>405</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269341</t>
+          <t>268863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275311</t>
+          <t>275307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3160</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12253</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15144</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>564056</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>558102</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>567195</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>771</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>513593</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>507805</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>517515</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>508191</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>517600</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>564056</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>558539</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>567203</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1071278</t>
+          <t>1070373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1083334</t>
+          <t>1083318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>786</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>522949</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>522949</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>522949</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5255</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4447</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5432</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6062</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54710</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53847</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50231</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45888</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41326</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,38%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59805</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55942</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61471</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113652</t>
+          <t>100598</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109116</t>
+          <t>95605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115812</t>
+          <t>102840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2369</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6523</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29841</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>112153</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178585</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>473309</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>469155</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>475177</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>430669</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>348357</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>458133</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,52%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>513956</t>
+          <t>426694</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509633</t>
+          <t>414686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515531</t>
+          <t>430429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>944625</t>
+          <t>900004</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>798544</t>
+          <t>888671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972242</t>
+          <t>904213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10477</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3333</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4880</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10289</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162022</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156416</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164990</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>148185</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>145462</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148795</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>148537</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146548</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149157</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>176827</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>171418</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>179836</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,34%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>458</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>325012</t>
+          <t>310559</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319427</t>
+          <t>305148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328114</t>
+          <t>313732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166893</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166893</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166893</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148795</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148795</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148795</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181707</t>
+          <t>149157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181707</t>
+          <t>149157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181707</t>
+          <t>149157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330502</t>
+          <t>316050</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330502</t>
+          <t>316050</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330502</t>
+          <t>316050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4997</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15865</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>121848</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157028</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>690042</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>683439</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>694307</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>632700</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>542134</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>660573</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>750589</t>
+          <t>621118</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744313</t>
+          <t>609621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754731</t>
+          <t>625237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1383289</t>
+          <t>1311160</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267284</t>
+          <t>1299251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1411421</t>
+          <t>1317506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663982</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663982</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663982</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628362</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424312</t>
+          <t>1327666</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424312</t>
+          <t>1327666</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424312</t>
+          <t>1327666</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
